--- a/тест-сбют на создание пользователя.xlsx
+++ b/тест-сбют на создание пользователя.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestProjectIntern_n1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693F5A1B-F611-4BD3-8E70-6768AFDE26B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B47DC3C-246F-42EE-97E4-CD058076BD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4E15E216-51A8-456E-934B-85F197B28B32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{4E15E216-51A8-456E-934B-85F197B28B32}"/>
   </bookViews>
   <sheets>
     <sheet name="Тест-кейс №1" sheetId="2" r:id="rId1"/>
     <sheet name="Тест-кейс №2" sheetId="3" r:id="rId2"/>
-    <sheet name="Лист1" sheetId="1" r:id="rId3"/>
+    <sheet name="Тест-кейс №3" sheetId="6" r:id="rId3"/>
+    <sheet name="Тест-кейс №4" sheetId="4" r:id="rId4"/>
+    <sheet name="Тест-кейс №5" sheetId="5" r:id="rId5"/>
+    <sheet name="Тест-кейс №6" sheetId="7" r:id="rId6"/>
+    <sheet name="Тест-кейс №7" sheetId="8" r:id="rId7"/>
+    <sheet name="Тест-кейс №8" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="50">
   <si>
     <t xml:space="preserve">2.  </t>
   </si>
@@ -201,6 +206,77 @@
   <si>
     <t xml:space="preserve">1. Вызвать endpoint PUT https://itester.online/auth/clients  с телом запроса который содержит address, birthdate, email, firstName, lastName, login, middleName, password, phoneNumber, sex
 </t>
+  </si>
+  <si>
+    <t>PUT запрос со статусом 422</t>
+  </si>
+  <si>
+    <t>провален</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/auth/clients  с sex:
+null
+"1234"
+"dfdgdg"
+"@#$$#"
+""</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/auth/clients  с email:
+null
+"1234"
+"dfdgdg"
+"@#$$#"
+""</t>
+  </si>
+  <si>
+    <t>Создание пользователя c невалидным sex
+Web API</t>
+  </si>
+  <si>
+    <t>Создание пользователя c невалидным c email
+Web API</t>
+  </si>
+  <si>
+    <t>Создание пользователя c невалидным login
+Web API</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/auth/clients  с login:
+null
+""</t>
+  </si>
+  <si>
+    <t>Создание пользователя с невалидным password
+Web API</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/auth/clients  с password:
+null
+""
+"123456dfsd"
+ "fkkoe454ldlsl343lssl5"</t>
+  </si>
+  <si>
+    <t>Создание пользователя с невалидным birthdate
+Web API</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/auth/clients  с password:
+null
+""
+"2020-12-03"</t>
+  </si>
+  <si>
+    <t>Создание пользователя с невалидным phonenumber
+Web API</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/auth/clients  с password:
+null
+""
+"+798756778980"
+"+67050-5"</t>
   </si>
 </sst>
 </file>
@@ -459,152 +535,155 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -939,198 +1018,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="46">
+      <c r="B1" s="35">
         <v>1</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="48"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="39" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="186.75" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="144.75" customHeight="1">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="19"/>
+      <c r="D16" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="127.5" customHeight="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="10"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
@@ -1140,6 +1219,13 @@
     <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="B15:C15"/>
@@ -1149,13 +1235,6 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B3:D3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{01D7EF88-4ECD-4853-95F7-F3158EF5849B}"/>
@@ -1182,186 +1261,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="46">
+      <c r="B1" s="35">
         <v>2</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="48"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="39" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="186.75" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="87.75" customHeight="1">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
     </row>
     <row r="18" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="49"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="49"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="49"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
@@ -1371,6 +1450,10 @@
     <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -1383,10 +1466,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{77293C4E-3F4C-42FB-AFFE-B07A3549C4F0}"/>
@@ -1398,10 +1477,1381 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106C29D4-C1FF-479E-AF7D-BC412409D4CF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9398E13C-DC03-4941-9F84-513DA8167351}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="35">
+        <v>3</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="186.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="87.75" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="1" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{3386DD46-CB41-4A7A-AE38-EAEA8B58F685}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{7F5F8AE4-8D3D-4F5B-8BDE-B94089E69552}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB784EAD-6803-4070-ABE9-5D2D04860F90}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="35">
+        <v>4</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="186.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="87.75" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="1" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{A907C619-CC18-4F2A-A8FB-C3CFFEB61561}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{8028C96E-C191-4543-AB48-E9C9144B76A5}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F52DD8-5559-4CD4-BFCD-54704DA9788E}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="35">
+        <v>5</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="186.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="87.75" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="1" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{0A33D7EC-E230-45AE-B5B2-719B60E425B2}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{531D27BF-1305-4CCD-908D-5CBAD2976526}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B722B6-98ED-480D-91FA-EEAC0BAFDF3B}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="35">
+        <v>6</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="186.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="87.75" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="1" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{462ABEB8-D2DB-49F1-AC6B-D45FF08A6CF9}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{D8FF0DC6-9BE8-4185-83E5-B6D59CD91B32}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D53FC41-176C-4DD1-9B77-A153299C204D}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="35">
+        <v>7</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="186.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="87.75" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="1" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{D615FE8D-9CEE-444A-A9A1-630871B4ABE7}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{49169854-3345-4118-92E6-E57E7E9E3DA9}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E631C1-182F-4D96-8E6B-2B6628289F94}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="35">
+        <v>8</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="34"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="186.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="87.75" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="1" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{C5AC51E1-389B-45DA-8D09-4D955AB7985A}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{C7B6B202-5308-47F8-8B40-C62C3CDE9043}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>